--- a/artfynd/A 37550-2026 artfynd.xlsx
+++ b/artfynd/A 37550-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137112312</v>
       </c>
       <c r="B2" t="n">
-        <v>92834</v>
+        <v>92840</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -770,7 +770,7 @@
         <v>0</v>
       </c>
       <c r="AE2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
@@ -799,7 +799,7 @@
         <v>137112280</v>
       </c>
       <c r="B3" t="n">
-        <v>92550</v>
+        <v>92556</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -911,7 +911,7 @@
         <v>137112282</v>
       </c>
       <c r="B4" t="n">
-        <v>92550</v>
+        <v>92556</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1135,7 +1135,7 @@
         <v>137112287</v>
       </c>
       <c r="B6" t="n">
-        <v>93088</v>
+        <v>93094</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1252,7 +1252,7 @@
         <v>137112297</v>
       </c>
       <c r="B7" t="n">
-        <v>93088</v>
+        <v>93094</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1364,7 +1364,7 @@
         <v>137112308</v>
       </c>
       <c r="B8" t="n">
-        <v>92081</v>
+        <v>92087</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -3288,7 +3288,7 @@
         <v>137112295</v>
       </c>
       <c r="B25" t="n">
-        <v>98230</v>
+        <v>98236</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3400,7 +3400,7 @@
         <v>137112304</v>
       </c>
       <c r="B26" t="n">
-        <v>99168</v>
+        <v>99174</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3512,7 +3512,7 @@
         <v>137112303</v>
       </c>
       <c r="B27" t="n">
-        <v>101462</v>
+        <v>101468</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/artfynd/A 37550-2026 artfynd.xlsx
+++ b/artfynd/A 37550-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137112312</v>
       </c>
       <c r="B2" t="n">
-        <v>92840</v>
+        <v>92844</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>137112280</v>
       </c>
       <c r="B3" t="n">
-        <v>92556</v>
+        <v>92560</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -911,7 +911,7 @@
         <v>137112282</v>
       </c>
       <c r="B4" t="n">
-        <v>92556</v>
+        <v>92560</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1023,7 +1023,7 @@
         <v>137112301</v>
       </c>
       <c r="B5" t="n">
-        <v>80599</v>
+        <v>80601</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1135,7 +1135,7 @@
         <v>137112287</v>
       </c>
       <c r="B6" t="n">
-        <v>93094</v>
+        <v>93098</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1252,7 +1252,7 @@
         <v>137112297</v>
       </c>
       <c r="B7" t="n">
-        <v>93094</v>
+        <v>93098</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1364,7 +1364,7 @@
         <v>137112308</v>
       </c>
       <c r="B8" t="n">
-        <v>92087</v>
+        <v>92091</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1476,7 +1476,7 @@
         <v>137112278</v>
       </c>
       <c r="B9" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1588,7 +1588,7 @@
         <v>137112285</v>
       </c>
       <c r="B10" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1700,7 +1700,7 @@
         <v>137112286</v>
       </c>
       <c r="B11" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1812,7 +1812,7 @@
         <v>137112283</v>
       </c>
       <c r="B12" t="n">
-        <v>80598</v>
+        <v>80600</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1924,7 +1924,7 @@
         <v>137112293</v>
       </c>
       <c r="B13" t="n">
-        <v>80598</v>
+        <v>80600</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2036,7 +2036,7 @@
         <v>137112300</v>
       </c>
       <c r="B14" t="n">
-        <v>80598</v>
+        <v>80600</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2148,7 +2148,7 @@
         <v>137112296</v>
       </c>
       <c r="B15" t="n">
-        <v>80609</v>
+        <v>80611</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2260,7 +2260,7 @@
         <v>137112302</v>
       </c>
       <c r="B16" t="n">
-        <v>80609</v>
+        <v>80611</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2372,7 +2372,7 @@
         <v>137112305</v>
       </c>
       <c r="B17" t="n">
-        <v>80609</v>
+        <v>80611</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -3288,7 +3288,7 @@
         <v>137112295</v>
       </c>
       <c r="B25" t="n">
-        <v>98236</v>
+        <v>98240</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3400,7 +3400,7 @@
         <v>137112304</v>
       </c>
       <c r="B26" t="n">
-        <v>99174</v>
+        <v>99178</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3512,7 +3512,7 @@
         <v>137112303</v>
       </c>
       <c r="B27" t="n">
-        <v>101468</v>
+        <v>101472</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/artfynd/A 37550-2026 artfynd.xlsx
+++ b/artfynd/A 37550-2026 artfynd.xlsx
@@ -3288,7 +3288,7 @@
         <v>137112295</v>
       </c>
       <c r="B25" t="n">
-        <v>98240</v>
+        <v>98242</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3400,7 +3400,7 @@
         <v>137112304</v>
       </c>
       <c r="B26" t="n">
-        <v>99178</v>
+        <v>99180</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3512,7 +3512,7 @@
         <v>137112303</v>
       </c>
       <c r="B27" t="n">
-        <v>101472</v>
+        <v>101474</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/artfynd/A 37550-2026 artfynd.xlsx
+++ b/artfynd/A 37550-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137112312</v>
       </c>
       <c r="B2" t="n">
-        <v>92844</v>
+        <v>92846</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>137112280</v>
       </c>
       <c r="B3" t="n">
-        <v>92560</v>
+        <v>92562</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -911,7 +911,7 @@
         <v>137112282</v>
       </c>
       <c r="B4" t="n">
-        <v>92560</v>
+        <v>92562</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1023,7 +1023,7 @@
         <v>137112301</v>
       </c>
       <c r="B5" t="n">
-        <v>80601</v>
+        <v>80604</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1135,7 +1135,7 @@
         <v>137112287</v>
       </c>
       <c r="B6" t="n">
-        <v>93098</v>
+        <v>93100</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1252,7 +1252,7 @@
         <v>137112297</v>
       </c>
       <c r="B7" t="n">
-        <v>93098</v>
+        <v>93100</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1364,7 +1364,7 @@
         <v>137112308</v>
       </c>
       <c r="B8" t="n">
-        <v>92091</v>
+        <v>92093</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1476,7 +1476,7 @@
         <v>137112278</v>
       </c>
       <c r="B9" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1588,7 +1588,7 @@
         <v>137112285</v>
       </c>
       <c r="B10" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1700,7 +1700,7 @@
         <v>137112286</v>
       </c>
       <c r="B11" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1812,7 +1812,7 @@
         <v>137112283</v>
       </c>
       <c r="B12" t="n">
-        <v>80600</v>
+        <v>80603</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1924,7 +1924,7 @@
         <v>137112293</v>
       </c>
       <c r="B13" t="n">
-        <v>80600</v>
+        <v>80603</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2021,7 +2021,7 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Alice Thomander, Tintin Almqvist, Sofia Eng, Elvira  Hahn Nilsson</t>
+          <t>Alice Thomander, Sofia Eng, Elvira  Hahn Nilsson , Tintin Almqvist</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
@@ -2036,7 +2036,7 @@
         <v>137112300</v>
       </c>
       <c r="B14" t="n">
-        <v>80600</v>
+        <v>80603</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2148,7 +2148,7 @@
         <v>137112296</v>
       </c>
       <c r="B15" t="n">
-        <v>80611</v>
+        <v>80614</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2260,7 +2260,7 @@
         <v>137112302</v>
       </c>
       <c r="B16" t="n">
-        <v>80611</v>
+        <v>80614</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2372,7 +2372,7 @@
         <v>137112305</v>
       </c>
       <c r="B17" t="n">
-        <v>80611</v>
+        <v>80614</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -3288,7 +3288,7 @@
         <v>137112295</v>
       </c>
       <c r="B25" t="n">
-        <v>98242</v>
+        <v>98244</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3400,7 +3400,7 @@
         <v>137112304</v>
       </c>
       <c r="B26" t="n">
-        <v>99180</v>
+        <v>99182</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3512,7 +3512,7 @@
         <v>137112303</v>
       </c>
       <c r="B27" t="n">
-        <v>101474</v>
+        <v>101476</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3609,7 +3609,7 @@
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Alice Thomander, Tintin Almqvist, Sofia Eng, Elvira  Hahn Nilsson</t>
+          <t>Alice Thomander, Elvira  Hahn Nilsson , Tintin Almqvist, Sofia Eng</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>

--- a/artfynd/A 37550-2026 artfynd.xlsx
+++ b/artfynd/A 37550-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137112312</v>
       </c>
       <c r="B2" t="n">
-        <v>92846</v>
+        <v>92859</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>137112280</v>
       </c>
       <c r="B3" t="n">
-        <v>92562</v>
+        <v>92575</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -911,7 +911,7 @@
         <v>137112282</v>
       </c>
       <c r="B4" t="n">
-        <v>92562</v>
+        <v>92575</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1023,7 +1023,7 @@
         <v>137112301</v>
       </c>
       <c r="B5" t="n">
-        <v>80604</v>
+        <v>80617</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1135,7 +1135,7 @@
         <v>137112287</v>
       </c>
       <c r="B6" t="n">
-        <v>93100</v>
+        <v>93113</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1252,7 +1252,7 @@
         <v>137112297</v>
       </c>
       <c r="B7" t="n">
-        <v>93100</v>
+        <v>93113</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1364,7 +1364,7 @@
         <v>137112308</v>
       </c>
       <c r="B8" t="n">
-        <v>92093</v>
+        <v>92106</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1476,7 +1476,7 @@
         <v>137112278</v>
       </c>
       <c r="B9" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1588,7 +1588,7 @@
         <v>137112285</v>
       </c>
       <c r="B10" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1700,7 +1700,7 @@
         <v>137112286</v>
       </c>
       <c r="B11" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1812,7 +1812,7 @@
         <v>137112283</v>
       </c>
       <c r="B12" t="n">
-        <v>80603</v>
+        <v>80616</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1924,7 +1924,7 @@
         <v>137112293</v>
       </c>
       <c r="B13" t="n">
-        <v>80603</v>
+        <v>80616</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2021,7 +2021,7 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Alice Thomander, Sofia Eng, Elvira  Hahn Nilsson , Tintin Almqvist</t>
+          <t>Alice Thomander, Tintin Almqvist, Sofia Eng, Elvira  Hahn Nilsson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
@@ -2036,7 +2036,7 @@
         <v>137112300</v>
       </c>
       <c r="B14" t="n">
-        <v>80603</v>
+        <v>80616</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2148,7 +2148,7 @@
         <v>137112296</v>
       </c>
       <c r="B15" t="n">
-        <v>80614</v>
+        <v>80627</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2260,7 +2260,7 @@
         <v>137112302</v>
       </c>
       <c r="B16" t="n">
-        <v>80614</v>
+        <v>80627</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2372,7 +2372,7 @@
         <v>137112305</v>
       </c>
       <c r="B17" t="n">
-        <v>80614</v>
+        <v>80627</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2484,7 +2484,7 @@
         <v>137112292</v>
       </c>
       <c r="B18" t="n">
-        <v>58005</v>
+        <v>58018</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2601,7 +2601,7 @@
         <v>137112306</v>
       </c>
       <c r="B19" t="n">
-        <v>58005</v>
+        <v>58018</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2718,7 +2718,7 @@
         <v>137112284</v>
       </c>
       <c r="B20" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2835,7 +2835,7 @@
         <v>137112288</v>
       </c>
       <c r="B21" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2952,7 +2952,7 @@
         <v>137112323</v>
       </c>
       <c r="B22" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3064,7 +3064,7 @@
         <v>137112309</v>
       </c>
       <c r="B23" t="n">
-        <v>58112</v>
+        <v>58125</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3176,7 +3176,7 @@
         <v>137112311</v>
       </c>
       <c r="B24" t="n">
-        <v>56739</v>
+        <v>56752</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3288,7 +3288,7 @@
         <v>137112295</v>
       </c>
       <c r="B25" t="n">
-        <v>98244</v>
+        <v>98257</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3400,7 +3400,7 @@
         <v>137112304</v>
       </c>
       <c r="B26" t="n">
-        <v>99182</v>
+        <v>99195</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3512,7 +3512,7 @@
         <v>137112303</v>
       </c>
       <c r="B27" t="n">
-        <v>101476</v>
+        <v>101489</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3609,7 +3609,7 @@
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Alice Thomander, Elvira  Hahn Nilsson , Tintin Almqvist, Sofia Eng</t>
+          <t>Alice Thomander, Tintin Almqvist, Sofia Eng, Elvira  Hahn Nilsson</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>

--- a/artfynd/A 37550-2026 artfynd.xlsx
+++ b/artfynd/A 37550-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137112312</v>
       </c>
       <c r="B2" t="n">
-        <v>92859</v>
+        <v>92861</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>137112280</v>
       </c>
       <c r="B3" t="n">
-        <v>92575</v>
+        <v>92577</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -911,7 +911,7 @@
         <v>137112282</v>
       </c>
       <c r="B4" t="n">
-        <v>92575</v>
+        <v>92577</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1023,7 +1023,7 @@
         <v>137112301</v>
       </c>
       <c r="B5" t="n">
-        <v>80617</v>
+        <v>80619</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1135,7 +1135,7 @@
         <v>137112287</v>
       </c>
       <c r="B6" t="n">
-        <v>93113</v>
+        <v>93115</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1252,7 +1252,7 @@
         <v>137112297</v>
       </c>
       <c r="B7" t="n">
-        <v>93113</v>
+        <v>93115</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1364,7 +1364,7 @@
         <v>137112308</v>
       </c>
       <c r="B8" t="n">
-        <v>92106</v>
+        <v>92108</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1476,7 +1476,7 @@
         <v>137112278</v>
       </c>
       <c r="B9" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1588,7 +1588,7 @@
         <v>137112285</v>
       </c>
       <c r="B10" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1700,7 +1700,7 @@
         <v>137112286</v>
       </c>
       <c r="B11" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1812,7 +1812,7 @@
         <v>137112283</v>
       </c>
       <c r="B12" t="n">
-        <v>80616</v>
+        <v>80618</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1924,7 +1924,7 @@
         <v>137112293</v>
       </c>
       <c r="B13" t="n">
-        <v>80616</v>
+        <v>80618</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2036,7 +2036,7 @@
         <v>137112300</v>
       </c>
       <c r="B14" t="n">
-        <v>80616</v>
+        <v>80618</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2148,7 +2148,7 @@
         <v>137112296</v>
       </c>
       <c r="B15" t="n">
-        <v>80627</v>
+        <v>80629</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2260,7 +2260,7 @@
         <v>137112302</v>
       </c>
       <c r="B16" t="n">
-        <v>80627</v>
+        <v>80629</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2372,7 +2372,7 @@
         <v>137112305</v>
       </c>
       <c r="B17" t="n">
-        <v>80627</v>
+        <v>80629</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2484,7 +2484,7 @@
         <v>137112292</v>
       </c>
       <c r="B18" t="n">
-        <v>58018</v>
+        <v>58020</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2601,7 +2601,7 @@
         <v>137112306</v>
       </c>
       <c r="B19" t="n">
-        <v>58018</v>
+        <v>58020</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2718,7 +2718,7 @@
         <v>137112284</v>
       </c>
       <c r="B20" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2835,7 +2835,7 @@
         <v>137112288</v>
       </c>
       <c r="B21" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2952,7 +2952,7 @@
         <v>137112323</v>
       </c>
       <c r="B22" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3064,7 +3064,7 @@
         <v>137112309</v>
       </c>
       <c r="B23" t="n">
-        <v>58125</v>
+        <v>58127</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3176,7 +3176,7 @@
         <v>137112311</v>
       </c>
       <c r="B24" t="n">
-        <v>56752</v>
+        <v>56754</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3288,7 +3288,7 @@
         <v>137112295</v>
       </c>
       <c r="B25" t="n">
-        <v>98257</v>
+        <v>98259</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3400,7 +3400,7 @@
         <v>137112304</v>
       </c>
       <c r="B26" t="n">
-        <v>99195</v>
+        <v>99197</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3512,7 +3512,7 @@
         <v>137112303</v>
       </c>
       <c r="B27" t="n">
-        <v>101489</v>
+        <v>101491</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/artfynd/A 37550-2026 artfynd.xlsx
+++ b/artfynd/A 37550-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ27"/>
+  <dimension ref="A1:AZ38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1020,10 +1020,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>137112301</v>
+        <v>137257148</v>
       </c>
       <c r="B5" t="n">
-        <v>80619</v>
+        <v>92580</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1031,21 +1031,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2081</v>
+        <v>1209</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1055,13 +1055,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>540045</v>
+        <v>540102</v>
       </c>
       <c r="R5" t="n">
-        <v>7206441</v>
+        <v>7206113</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1085,22 +1085,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1111,53 +1111,63 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, utan markontakt</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Horizontal, dead without ground contact</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Alice Thomander</t>
+          <t>Tintin Almqvist</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Alice Thomander, Tintin Almqvist, Sofia Eng, Elvira  Hahn Nilsson</t>
+          <t>Tintin Almqvist</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137112301</t>
+          <t>https://artportalen.se/Sighting/137257148</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>137112287</v>
+        <v>137112301</v>
       </c>
       <c r="B6" t="n">
-        <v>93115</v>
+        <v>80619</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4769</v>
+        <v>2081</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1167,10 +1177,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>540084</v>
+        <v>540045</v>
       </c>
       <c r="R6" t="n">
-        <v>7206223</v>
+        <v>7206441</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1202,7 +1212,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1212,12 +1222,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:16</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Okänd</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1243,16 +1248,16 @@
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137112287</t>
+          <t>https://artportalen.se/Sighting/137112301</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>137112297</v>
+        <v>137257150</v>
       </c>
       <c r="B7" t="n">
-        <v>93115</v>
+        <v>96609</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1260,21 +1265,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4769</v>
+        <v>2809</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1284,13 +1289,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>540009</v>
+        <v>540258</v>
       </c>
       <c r="R7" t="n">
-        <v>7206346</v>
+        <v>7205854</v>
       </c>
       <c r="S7" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1314,22 +1319,22 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>16:04</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>16:04</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1344,27 +1349,27 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Alice Thomander</t>
+          <t>Tintin Almqvist</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Alice Thomander, Tintin Almqvist, Sofia Eng, Elvira  Hahn Nilsson</t>
+          <t>Tintin Almqvist</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137112297</t>
+          <t>https://artportalen.se/Sighting/137257150</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>137112308</v>
+        <v>137112287</v>
       </c>
       <c r="B8" t="n">
-        <v>92108</v>
+        <v>93115</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1372,21 +1377,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5447</v>
+        <v>4769</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1396,13 +1401,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>540218</v>
+        <v>540084</v>
       </c>
       <c r="R8" t="n">
-        <v>7206472</v>
+        <v>7206223</v>
       </c>
       <c r="S8" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1426,22 +1431,27 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>09:08</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>09:08</t>
+          <t>10:16</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Okänd</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1467,38 +1477,38 @@
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137112308</t>
+          <t>https://artportalen.se/Sighting/137112287</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>137112278</v>
+        <v>137112297</v>
       </c>
       <c r="B9" t="n">
-        <v>79503</v>
+        <v>93115</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>4769</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1508,13 +1518,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>540243</v>
+        <v>540009</v>
       </c>
       <c r="R9" t="n">
-        <v>7206088</v>
+        <v>7206346</v>
       </c>
       <c r="S9" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1538,22 +1548,22 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1579,38 +1589,38 @@
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137112278</t>
+          <t>https://artportalen.se/Sighting/137112297</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>137112285</v>
+        <v>137112308</v>
       </c>
       <c r="B10" t="n">
-        <v>79503</v>
+        <v>92108</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1620,13 +1630,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>540074</v>
+        <v>540218</v>
       </c>
       <c r="R10" t="n">
-        <v>7206204</v>
+        <v>7206472</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1650,22 +1660,22 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>09:08</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>09:08</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1691,13 +1701,13 @@
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137112285</t>
+          <t>https://artportalen.se/Sighting/137112308</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>137112286</v>
+        <v>137112278</v>
       </c>
       <c r="B11" t="n">
         <v>79503</v>
@@ -1732,10 +1742,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>540070</v>
+        <v>540243</v>
       </c>
       <c r="R11" t="n">
-        <v>7206181</v>
+        <v>7206088</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1762,22 +1772,22 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1803,38 +1813,38 @@
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137112286</t>
+          <t>https://artportalen.se/Sighting/137112278</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>137112283</v>
+        <v>137112285</v>
       </c>
       <c r="B12" t="n">
-        <v>80618</v>
+        <v>79503</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1844,10 +1854,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>540258</v>
+        <v>540074</v>
       </c>
       <c r="R12" t="n">
-        <v>7205874</v>
+        <v>7206204</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1874,22 +1884,22 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1915,38 +1925,38 @@
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137112283</t>
+          <t>https://artportalen.se/Sighting/137112285</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>137112293</v>
+        <v>137112286</v>
       </c>
       <c r="B13" t="n">
-        <v>80618</v>
+        <v>79503</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1956,13 +1966,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>540014</v>
+        <v>540070</v>
       </c>
       <c r="R13" t="n">
-        <v>7206373</v>
+        <v>7206181</v>
       </c>
       <c r="S13" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1991,7 +2001,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2001,7 +2011,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2027,54 +2037,63 @@
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137112293</t>
+          <t>https://artportalen.se/Sighting/137112286</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>137112300</v>
+        <v>137257147</v>
       </c>
       <c r="B14" t="n">
-        <v>80618</v>
+        <v>79503</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Dorris, Ås lm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>540041</v>
+        <v>540112</v>
       </c>
       <c r="R14" t="n">
-        <v>7206439</v>
+        <v>7206114</v>
       </c>
       <c r="S14" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2098,22 +2117,27 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>14:46</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>På cirka 10 träd</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2128,44 +2152,44 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Alice Thomander</t>
+          <t>Tintin Almqvist</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Alice Thomander, Tintin Almqvist, Sofia Eng, Elvira  Hahn Nilsson</t>
+          <t>Tintin Almqvist</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137112300</t>
+          <t>https://artportalen.se/Sighting/137257147</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>137112296</v>
+        <v>137257153</v>
       </c>
       <c r="B15" t="n">
-        <v>80629</v>
+        <v>79503</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6463</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -2173,20 +2197,29 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr"/>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Dorris, Ås lm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>540009</v>
+        <v>540326</v>
       </c>
       <c r="R15" t="n">
-        <v>7206371</v>
+        <v>7205811</v>
       </c>
       <c r="S15" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2215,7 +2248,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2225,7 +2258,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2240,49 +2273,49 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Alice Thomander</t>
+          <t>Tintin Almqvist</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Alice Thomander, Tintin Almqvist, Sofia Eng, Elvira  Hahn Nilsson</t>
+          <t>Tintin Almqvist</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137112296</t>
+          <t>https://artportalen.se/Sighting/137257153</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>137112302</v>
+        <v>137112283</v>
       </c>
       <c r="B16" t="n">
-        <v>80629</v>
+        <v>80618</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6463</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2292,13 +2325,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>539996</v>
+        <v>540258</v>
       </c>
       <c r="R16" t="n">
-        <v>7206554</v>
+        <v>7205874</v>
       </c>
       <c r="S16" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2322,22 +2355,22 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2363,38 +2396,38 @@
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137112302</t>
+          <t>https://artportalen.se/Sighting/137112283</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>137112305</v>
+        <v>137112293</v>
       </c>
       <c r="B17" t="n">
-        <v>80629</v>
+        <v>80618</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6463</v>
+        <v>6458</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2404,13 +2437,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>540184</v>
+        <v>540014</v>
       </c>
       <c r="R17" t="n">
-        <v>7206432</v>
+        <v>7206373</v>
       </c>
       <c r="S17" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2434,22 +2467,22 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>08:53</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>08:53</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2475,38 +2508,38 @@
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137112305</t>
+          <t>https://artportalen.se/Sighting/137112293</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>137112292</v>
+        <v>137112300</v>
       </c>
       <c r="B18" t="n">
-        <v>58020</v>
+        <v>80618</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2516,13 +2549,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>540045</v>
+        <v>540041</v>
       </c>
       <c r="R18" t="n">
-        <v>7206325</v>
+        <v>7206439</v>
       </c>
       <c r="S18" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2551,7 +2584,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2561,12 +2594,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>10:45</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Hack</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2592,54 +2620,63 @@
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137112292</t>
+          <t>https://artportalen.se/Sighting/137112300</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>137112306</v>
+        <v>137257152</v>
       </c>
       <c r="B19" t="n">
-        <v>58020</v>
+        <v>80618</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Dorris, Ås lm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>540199</v>
+        <v>540257</v>
       </c>
       <c r="R19" t="n">
-        <v>7206483</v>
+        <v>7205846</v>
       </c>
       <c r="S19" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2663,27 +2700,22 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>16:08</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>09:01</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Hackspår</t>
+          <t>16:08</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2698,49 +2730,49 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Alice Thomander</t>
+          <t>Tintin Almqvist</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Alice Thomander, Tintin Almqvist, Sofia Eng, Elvira  Hahn Nilsson</t>
+          <t>Tintin Almqvist</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137112306</t>
+          <t>https://artportalen.se/Sighting/137257152</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>137112284</v>
+        <v>137112296</v>
       </c>
       <c r="B20" t="n">
-        <v>58023</v>
+        <v>80629</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>6463</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2750,13 +2782,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>540201</v>
+        <v>540009</v>
       </c>
       <c r="R20" t="n">
-        <v>7206150</v>
+        <v>7206371</v>
       </c>
       <c r="S20" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2785,7 +2817,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>09:35</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2795,12 +2827,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>09:35</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2826,38 +2853,38 @@
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137112284</t>
+          <t>https://artportalen.se/Sighting/137112296</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>137112288</v>
+        <v>137112302</v>
       </c>
       <c r="B21" t="n">
-        <v>58023</v>
+        <v>80629</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>6463</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2867,10 +2894,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>540075</v>
+        <v>539996</v>
       </c>
       <c r="R21" t="n">
-        <v>7206224</v>
+        <v>7206554</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2902,7 +2929,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>10:18</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2912,12 +2939,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>10:18</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2943,38 +2965,38 @@
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137112288</t>
+          <t>https://artportalen.se/Sighting/137112302</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>137112323</v>
+        <v>137112305</v>
       </c>
       <c r="B22" t="n">
-        <v>58023</v>
+        <v>80629</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>6463</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2984,10 +3006,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>540237</v>
+        <v>540184</v>
       </c>
       <c r="R22" t="n">
-        <v>7206086</v>
+        <v>7206432</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -3019,7 +3041,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>08:53</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3029,7 +3051,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>08:53</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3055,38 +3077,38 @@
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137112323</t>
+          <t>https://artportalen.se/Sighting/137112305</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>137112309</v>
+        <v>137257157</v>
       </c>
       <c r="B23" t="n">
-        <v>58127</v>
+        <v>80629</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>103031</v>
+        <v>6463</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3096,13 +3118,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>540231</v>
+        <v>540009</v>
       </c>
       <c r="R23" t="n">
-        <v>7206472</v>
+        <v>7206419</v>
       </c>
       <c r="S23" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3126,22 +3148,27 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>12:36</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>På sälg</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3152,53 +3179,63 @@
       </c>
       <c r="AG23" t="b">
         <v>0</v>
+      </c>
+      <c r="AM23" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO23" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant</t>
+        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Alice Thomander</t>
+          <t>Tintin Almqvist</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Alice Thomander, Tintin Almqvist, Sofia Eng, Elvira  Hahn Nilsson</t>
+          <t>Tintin Almqvist</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137112309</t>
+          <t>https://artportalen.se/Sighting/137257157</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>137112311</v>
+        <v>137257158</v>
       </c>
       <c r="B24" t="n">
-        <v>56754</v>
+        <v>80630</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>206046</v>
+        <v>6464</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Älg</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alces alces</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3208,13 +3245,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>540097</v>
+        <v>540002</v>
       </c>
       <c r="R24" t="n">
-        <v>7206552</v>
+        <v>7206435</v>
       </c>
       <c r="S24" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3238,22 +3275,27 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>12:48</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>På sälg</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3264,31 +3306,41 @@
       </c>
       <c r="AG24" t="b">
         <v>0</v>
+      </c>
+      <c r="AM24" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO24" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant</t>
+        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Alice Thomander</t>
+          <t>Tintin Almqvist</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Alice Thomander, Tintin Almqvist, Sofia Eng, Elvira  Hahn Nilsson</t>
+          <t>Tintin Almqvist</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137112311</t>
+          <t>https://artportalen.se/Sighting/137257158</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>137112295</v>
+        <v>137112292</v>
       </c>
       <c r="B25" t="n">
-        <v>98259</v>
+        <v>58020</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3296,21 +3348,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>221941</v>
+        <v>100049</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3320,13 +3372,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>540009</v>
+        <v>540045</v>
       </c>
       <c r="R25" t="n">
-        <v>7206371</v>
+        <v>7206325</v>
       </c>
       <c r="S25" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3355,7 +3407,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3365,7 +3417,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:45</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3391,16 +3448,16 @@
       <c r="AY25" t="inlineStr"/>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137112295</t>
+          <t>https://artportalen.se/Sighting/137112292</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>137112304</v>
+        <v>137112306</v>
       </c>
       <c r="B26" t="n">
-        <v>99197</v>
+        <v>58020</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3408,21 +3465,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>223049</v>
+        <v>100049</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ormbär</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Paris quadrifolia</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3432,10 +3489,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>539959</v>
+        <v>540199</v>
       </c>
       <c r="R26" t="n">
-        <v>7206577</v>
+        <v>7206483</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3462,22 +3519,27 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>09:01</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Hackspår</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3503,38 +3565,38 @@
       <c r="AY26" t="inlineStr"/>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137112304</t>
+          <t>https://artportalen.se/Sighting/137112306</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>137112303</v>
+        <v>137112284</v>
       </c>
       <c r="B27" t="n">
-        <v>101491</v>
+        <v>58023</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>224885</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Nordisk stormhatt</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Aconitum lycoctonum subsp. septentrionale</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Koelle) Korsh.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3544,13 +3606,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>539971</v>
+        <v>540201</v>
       </c>
       <c r="R27" t="n">
-        <v>7206576</v>
+        <v>7206150</v>
       </c>
       <c r="S27" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3579,7 +3641,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3589,7 +3651,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>09:35</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3614,6 +3681,1255 @@
       </c>
       <c r="AY27" t="inlineStr"/>
       <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137112284</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>137112288</v>
+      </c>
+      <c r="B28" t="n">
+        <v>58023</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Dorris, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>540075</v>
+      </c>
+      <c r="R28" t="n">
+        <v>7206224</v>
+      </c>
+      <c r="S28" t="n">
+        <v>5</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>10:18</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>10:18</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Alice Thomander</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Alice Thomander, Tintin Almqvist, Sofia Eng, Elvira  Hahn Nilsson</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137112288</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>137112323</v>
+      </c>
+      <c r="B29" t="n">
+        <v>58023</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Dorris, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>540237</v>
+      </c>
+      <c r="R29" t="n">
+        <v>7206086</v>
+      </c>
+      <c r="S29" t="n">
+        <v>5</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>13:57</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>13:57</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Alice Thomander</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Alice Thomander, Tintin Almqvist, Sofia Eng, Elvira  Hahn Nilsson</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137112323</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>137257154</v>
+      </c>
+      <c r="B30" t="n">
+        <v>58023</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="M30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Dorris, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>540327</v>
+      </c>
+      <c r="R30" t="n">
+        <v>7205790</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>09:50</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>09:50</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Tintin Almqvist</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Tintin Almqvist</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137257154</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>137257155</v>
+      </c>
+      <c r="B31" t="n">
+        <v>58023</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="M31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Dorris, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>540353</v>
+      </c>
+      <c r="R31" t="n">
+        <v>7205749</v>
+      </c>
+      <c r="S31" t="n">
+        <v>10</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>09:52</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>09:52</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Tintin Almqvist</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Tintin Almqvist</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137257155</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>137257156</v>
+      </c>
+      <c r="B32" t="n">
+        <v>58184</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Dorris, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>540353</v>
+      </c>
+      <c r="R32" t="n">
+        <v>7205749</v>
+      </c>
+      <c r="S32" t="n">
+        <v>10</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>09:55</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>09:55</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Tintin Almqvist</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Tintin Almqvist</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137257156</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>137112309</v>
+      </c>
+      <c r="B33" t="n">
+        <v>58127</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>103031</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Lavskrika</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Perisoreus infaustus</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Dorris, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>540231</v>
+      </c>
+      <c r="R33" t="n">
+        <v>7206472</v>
+      </c>
+      <c r="S33" t="n">
+        <v>15</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>09:11</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>09:11</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Alice Thomander</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Alice Thomander, Tintin Almqvist, Sofia Eng, Elvira  Hahn Nilsson</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137112309</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>137112311</v>
+      </c>
+      <c r="B34" t="n">
+        <v>56754</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>206046</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Älg</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Alces alces</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Dorris, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>540097</v>
+      </c>
+      <c r="R34" t="n">
+        <v>7206552</v>
+      </c>
+      <c r="S34" t="n">
+        <v>7</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>10:16</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>10:16</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Alice Thomander</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Alice Thomander, Tintin Almqvist, Sofia Eng, Elvira  Hahn Nilsson</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137112311</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>137257151</v>
+      </c>
+      <c r="B35" t="n">
+        <v>106521</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>221725</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Ögonpyrola</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Moneses uniflora</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(L.) A. Gray</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Dorris, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>540286</v>
+      </c>
+      <c r="R35" t="n">
+        <v>7205864</v>
+      </c>
+      <c r="S35" t="n">
+        <v>10</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>16:06</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>16:06</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Tintin Almqvist</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Tintin Almqvist</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137257151</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>137112295</v>
+      </c>
+      <c r="B36" t="n">
+        <v>98259</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>221941</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Plattlummer</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Lycopodium complanatum</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Dorris, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>540009</v>
+      </c>
+      <c r="R36" t="n">
+        <v>7206371</v>
+      </c>
+      <c r="S36" t="n">
+        <v>5</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Alice Thomander</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Alice Thomander, Tintin Almqvist, Sofia Eng, Elvira  Hahn Nilsson</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137112295</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>137112304</v>
+      </c>
+      <c r="B37" t="n">
+        <v>99197</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>223049</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Ormbär</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Paris quadrifolia</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Dorris, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>539959</v>
+      </c>
+      <c r="R37" t="n">
+        <v>7206577</v>
+      </c>
+      <c r="S37" t="n">
+        <v>5</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>13:13</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>13:13</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Alice Thomander</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Alice Thomander, Tintin Almqvist, Sofia Eng, Elvira  Hahn Nilsson</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137112304</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>137112303</v>
+      </c>
+      <c r="B38" t="n">
+        <v>101491</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>224885</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Nordisk stormhatt</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Aconitum lycoctonum subsp. septentrionale</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(Koelle) Korsh.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Dorris, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>539971</v>
+      </c>
+      <c r="R38" t="n">
+        <v>7206576</v>
+      </c>
+      <c r="S38" t="n">
+        <v>9</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>12:59</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>12:59</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Alice Thomander</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Alice Thomander, Tintin Almqvist, Sofia Eng, Elvira  Hahn Nilsson</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/137112303</t>
         </is>
@@ -3647,6 +4963,17 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 37550-2026 artfynd.xlsx
+++ b/artfynd/A 37550-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137112312</v>
       </c>
       <c r="B2" t="n">
-        <v>92861</v>
+        <v>92864</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>137112280</v>
       </c>
       <c r="B3" t="n">
-        <v>92577</v>
+        <v>92580</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -911,7 +911,7 @@
         <v>137112282</v>
       </c>
       <c r="B4" t="n">
-        <v>92577</v>
+        <v>92580</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1369,7 +1369,7 @@
         <v>137112287</v>
       </c>
       <c r="B8" t="n">
-        <v>93115</v>
+        <v>93118</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1486,7 +1486,7 @@
         <v>137112297</v>
       </c>
       <c r="B9" t="n">
-        <v>93115</v>
+        <v>93118</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1598,7 +1598,7 @@
         <v>137112308</v>
       </c>
       <c r="B10" t="n">
-        <v>92108</v>
+        <v>92111</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -4604,7 +4604,7 @@
         <v>137112295</v>
       </c>
       <c r="B36" t="n">
-        <v>98259</v>
+        <v>98262</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4716,7 +4716,7 @@
         <v>137112304</v>
       </c>
       <c r="B37" t="n">
-        <v>99197</v>
+        <v>99200</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4828,7 +4828,7 @@
         <v>137112303</v>
       </c>
       <c r="B38" t="n">
-        <v>101491</v>
+        <v>101494</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>

--- a/artfynd/A 37550-2026 artfynd.xlsx
+++ b/artfynd/A 37550-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137112312</v>
       </c>
       <c r="B2" t="n">
-        <v>92864</v>
+        <v>92874</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>137112280</v>
       </c>
       <c r="B3" t="n">
-        <v>92580</v>
+        <v>92590</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -911,7 +911,7 @@
         <v>137112282</v>
       </c>
       <c r="B4" t="n">
-        <v>92580</v>
+        <v>92590</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1023,7 +1023,7 @@
         <v>137257148</v>
       </c>
       <c r="B5" t="n">
-        <v>92580</v>
+        <v>92590</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1145,7 +1145,7 @@
         <v>137112301</v>
       </c>
       <c r="B6" t="n">
-        <v>80619</v>
+        <v>80629</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1257,7 +1257,7 @@
         <v>137257150</v>
       </c>
       <c r="B7" t="n">
-        <v>96609</v>
+        <v>96619</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1369,7 +1369,7 @@
         <v>137112287</v>
       </c>
       <c r="B8" t="n">
-        <v>93118</v>
+        <v>93128</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1486,7 +1486,7 @@
         <v>137112297</v>
       </c>
       <c r="B9" t="n">
-        <v>93118</v>
+        <v>93128</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1598,7 +1598,7 @@
         <v>137112308</v>
       </c>
       <c r="B10" t="n">
-        <v>92111</v>
+        <v>92121</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1710,7 +1710,7 @@
         <v>137112278</v>
       </c>
       <c r="B11" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1822,7 +1822,7 @@
         <v>137112285</v>
       </c>
       <c r="B12" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1934,7 +1934,7 @@
         <v>137112286</v>
       </c>
       <c r="B13" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2046,7 +2046,7 @@
         <v>137257147</v>
       </c>
       <c r="B14" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2172,7 +2172,7 @@
         <v>137257153</v>
       </c>
       <c r="B15" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2293,7 +2293,7 @@
         <v>137112283</v>
       </c>
       <c r="B16" t="n">
-        <v>80618</v>
+        <v>80628</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2405,7 +2405,7 @@
         <v>137112293</v>
       </c>
       <c r="B17" t="n">
-        <v>80618</v>
+        <v>80628</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2517,7 +2517,7 @@
         <v>137112300</v>
       </c>
       <c r="B18" t="n">
-        <v>80618</v>
+        <v>80628</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2629,7 +2629,7 @@
         <v>137257152</v>
       </c>
       <c r="B19" t="n">
-        <v>80618</v>
+        <v>80628</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2750,7 +2750,7 @@
         <v>137112296</v>
       </c>
       <c r="B20" t="n">
-        <v>80629</v>
+        <v>80639</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2862,7 +2862,7 @@
         <v>137112302</v>
       </c>
       <c r="B21" t="n">
-        <v>80629</v>
+        <v>80639</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2974,7 +2974,7 @@
         <v>137112305</v>
       </c>
       <c r="B22" t="n">
-        <v>80629</v>
+        <v>80639</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3086,7 +3086,7 @@
         <v>137257157</v>
       </c>
       <c r="B23" t="n">
-        <v>80629</v>
+        <v>80639</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3213,7 +3213,7 @@
         <v>137257158</v>
       </c>
       <c r="B24" t="n">
-        <v>80630</v>
+        <v>80640</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3340,7 +3340,7 @@
         <v>137112292</v>
       </c>
       <c r="B25" t="n">
-        <v>58020</v>
+        <v>58030</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3457,7 +3457,7 @@
         <v>137112306</v>
       </c>
       <c r="B26" t="n">
-        <v>58020</v>
+        <v>58030</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3574,7 +3574,7 @@
         <v>137112284</v>
       </c>
       <c r="B27" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3691,7 +3691,7 @@
         <v>137112288</v>
       </c>
       <c r="B28" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3808,7 +3808,7 @@
         <v>137112323</v>
       </c>
       <c r="B29" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3920,7 +3920,7 @@
         <v>137257154</v>
       </c>
       <c r="B30" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4033,7 +4033,7 @@
         <v>137257155</v>
       </c>
       <c r="B31" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4151,7 +4151,7 @@
         <v>137257156</v>
       </c>
       <c r="B32" t="n">
-        <v>58184</v>
+        <v>58194</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4268,7 +4268,7 @@
         <v>137112309</v>
       </c>
       <c r="B33" t="n">
-        <v>58127</v>
+        <v>58137</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4380,7 +4380,7 @@
         <v>137112311</v>
       </c>
       <c r="B34" t="n">
-        <v>56754</v>
+        <v>56764</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4492,7 +4492,7 @@
         <v>137257151</v>
       </c>
       <c r="B35" t="n">
-        <v>106521</v>
+        <v>106541</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4604,7 +4604,7 @@
         <v>137112295</v>
       </c>
       <c r="B36" t="n">
-        <v>98262</v>
+        <v>98272</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4716,7 +4716,7 @@
         <v>137112304</v>
       </c>
       <c r="B37" t="n">
-        <v>99200</v>
+        <v>99210</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4828,7 +4828,7 @@
         <v>137112303</v>
       </c>
       <c r="B38" t="n">
-        <v>101494</v>
+        <v>101509</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>

--- a/artfynd/A 37550-2026 artfynd.xlsx
+++ b/artfynd/A 37550-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137112312</v>
       </c>
       <c r="B2" t="n">
-        <v>92874</v>
+        <v>92875</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>137112280</v>
       </c>
       <c r="B3" t="n">
-        <v>92590</v>
+        <v>92591</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -911,7 +911,7 @@
         <v>137112282</v>
       </c>
       <c r="B4" t="n">
-        <v>92590</v>
+        <v>92591</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1023,7 +1023,7 @@
         <v>137257148</v>
       </c>
       <c r="B5" t="n">
-        <v>92590</v>
+        <v>92591</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1257,7 +1257,7 @@
         <v>137257150</v>
       </c>
       <c r="B7" t="n">
-        <v>96619</v>
+        <v>96620</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1369,7 +1369,7 @@
         <v>137112287</v>
       </c>
       <c r="B8" t="n">
-        <v>93128</v>
+        <v>93129</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1486,7 +1486,7 @@
         <v>137112297</v>
       </c>
       <c r="B9" t="n">
-        <v>93128</v>
+        <v>93129</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1598,7 +1598,7 @@
         <v>137112308</v>
       </c>
       <c r="B10" t="n">
-        <v>92121</v>
+        <v>92122</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -4492,7 +4492,7 @@
         <v>137257151</v>
       </c>
       <c r="B35" t="n">
-        <v>106541</v>
+        <v>106542</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4604,7 +4604,7 @@
         <v>137112295</v>
       </c>
       <c r="B36" t="n">
-        <v>98272</v>
+        <v>98273</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4716,7 +4716,7 @@
         <v>137112304</v>
       </c>
       <c r="B37" t="n">
-        <v>99210</v>
+        <v>99211</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4828,7 +4828,7 @@
         <v>137112303</v>
       </c>
       <c r="B38" t="n">
-        <v>101509</v>
+        <v>101510</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>

--- a/artfynd/A 37550-2026 artfynd.xlsx
+++ b/artfynd/A 37550-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137112312</v>
       </c>
       <c r="B2" t="n">
-        <v>92875</v>
+        <v>92878</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>137112280</v>
       </c>
       <c r="B3" t="n">
-        <v>92591</v>
+        <v>92594</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -911,7 +911,7 @@
         <v>137112282</v>
       </c>
       <c r="B4" t="n">
-        <v>92591</v>
+        <v>92594</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1023,7 +1023,7 @@
         <v>137257148</v>
       </c>
       <c r="B5" t="n">
-        <v>92591</v>
+        <v>92594</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1145,7 +1145,7 @@
         <v>137112301</v>
       </c>
       <c r="B6" t="n">
-        <v>80629</v>
+        <v>80632</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1257,7 +1257,7 @@
         <v>137257150</v>
       </c>
       <c r="B7" t="n">
-        <v>96620</v>
+        <v>96625</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1369,7 +1369,7 @@
         <v>137112287</v>
       </c>
       <c r="B8" t="n">
-        <v>93129</v>
+        <v>93132</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1486,7 +1486,7 @@
         <v>137112297</v>
       </c>
       <c r="B9" t="n">
-        <v>93129</v>
+        <v>93132</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1598,7 +1598,7 @@
         <v>137112308</v>
       </c>
       <c r="B10" t="n">
-        <v>92122</v>
+        <v>92125</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1710,7 +1710,7 @@
         <v>137112278</v>
       </c>
       <c r="B11" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1822,7 +1822,7 @@
         <v>137112285</v>
       </c>
       <c r="B12" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1934,7 +1934,7 @@
         <v>137112286</v>
       </c>
       <c r="B13" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2046,7 +2046,7 @@
         <v>137257147</v>
       </c>
       <c r="B14" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2172,7 +2172,7 @@
         <v>137257153</v>
       </c>
       <c r="B15" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2293,7 +2293,7 @@
         <v>137112283</v>
       </c>
       <c r="B16" t="n">
-        <v>80628</v>
+        <v>80631</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2405,7 +2405,7 @@
         <v>137112293</v>
       </c>
       <c r="B17" t="n">
-        <v>80628</v>
+        <v>80631</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2517,7 +2517,7 @@
         <v>137112300</v>
       </c>
       <c r="B18" t="n">
-        <v>80628</v>
+        <v>80631</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2629,7 +2629,7 @@
         <v>137257152</v>
       </c>
       <c r="B19" t="n">
-        <v>80628</v>
+        <v>80631</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2750,7 +2750,7 @@
         <v>137112296</v>
       </c>
       <c r="B20" t="n">
-        <v>80639</v>
+        <v>80642</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2862,7 +2862,7 @@
         <v>137112302</v>
       </c>
       <c r="B21" t="n">
-        <v>80639</v>
+        <v>80642</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2974,7 +2974,7 @@
         <v>137112305</v>
       </c>
       <c r="B22" t="n">
-        <v>80639</v>
+        <v>80642</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3086,7 +3086,7 @@
         <v>137257157</v>
       </c>
       <c r="B23" t="n">
-        <v>80639</v>
+        <v>80642</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3213,7 +3213,7 @@
         <v>137257158</v>
       </c>
       <c r="B24" t="n">
-        <v>80640</v>
+        <v>80643</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3340,7 +3340,7 @@
         <v>137112292</v>
       </c>
       <c r="B25" t="n">
-        <v>58030</v>
+        <v>58031</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3457,7 +3457,7 @@
         <v>137112306</v>
       </c>
       <c r="B26" t="n">
-        <v>58030</v>
+        <v>58031</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3574,7 +3574,7 @@
         <v>137112284</v>
       </c>
       <c r="B27" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3691,7 +3691,7 @@
         <v>137112288</v>
       </c>
       <c r="B28" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3808,7 +3808,7 @@
         <v>137112323</v>
       </c>
       <c r="B29" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3920,7 +3920,7 @@
         <v>137257154</v>
       </c>
       <c r="B30" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4033,7 +4033,7 @@
         <v>137257155</v>
       </c>
       <c r="B31" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4151,7 +4151,7 @@
         <v>137257156</v>
       </c>
       <c r="B32" t="n">
-        <v>58194</v>
+        <v>58195</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4268,7 +4268,7 @@
         <v>137112309</v>
       </c>
       <c r="B33" t="n">
-        <v>58137</v>
+        <v>58138</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4380,7 +4380,7 @@
         <v>137112311</v>
       </c>
       <c r="B34" t="n">
-        <v>56764</v>
+        <v>56765</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4492,7 +4492,7 @@
         <v>137257151</v>
       </c>
       <c r="B35" t="n">
-        <v>106542</v>
+        <v>106547</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4604,7 +4604,7 @@
         <v>137112295</v>
       </c>
       <c r="B36" t="n">
-        <v>98273</v>
+        <v>98278</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4716,7 +4716,7 @@
         <v>137112304</v>
       </c>
       <c r="B37" t="n">
-        <v>99211</v>
+        <v>99216</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4828,7 +4828,7 @@
         <v>137112303</v>
       </c>
       <c r="B38" t="n">
-        <v>101510</v>
+        <v>101515</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>

--- a/artfynd/A 37550-2026 artfynd.xlsx
+++ b/artfynd/A 37550-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137112312</v>
       </c>
       <c r="B2" t="n">
-        <v>92878</v>
+        <v>92880</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>137112280</v>
       </c>
       <c r="B3" t="n">
-        <v>92594</v>
+        <v>92596</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -911,7 +911,7 @@
         <v>137112282</v>
       </c>
       <c r="B4" t="n">
-        <v>92594</v>
+        <v>92596</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1023,7 +1023,7 @@
         <v>137257148</v>
       </c>
       <c r="B5" t="n">
-        <v>92594</v>
+        <v>92596</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1257,7 +1257,7 @@
         <v>137257150</v>
       </c>
       <c r="B7" t="n">
-        <v>96625</v>
+        <v>96627</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1369,7 +1369,7 @@
         <v>137112287</v>
       </c>
       <c r="B8" t="n">
-        <v>93132</v>
+        <v>93134</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1486,7 +1486,7 @@
         <v>137112297</v>
       </c>
       <c r="B9" t="n">
-        <v>93132</v>
+        <v>93134</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1598,7 +1598,7 @@
         <v>137112308</v>
       </c>
       <c r="B10" t="n">
-        <v>92125</v>
+        <v>92127</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -4492,7 +4492,7 @@
         <v>137257151</v>
       </c>
       <c r="B35" t="n">
-        <v>106547</v>
+        <v>106550</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4604,7 +4604,7 @@
         <v>137112295</v>
       </c>
       <c r="B36" t="n">
-        <v>98278</v>
+        <v>98280</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4716,7 +4716,7 @@
         <v>137112304</v>
       </c>
       <c r="B37" t="n">
-        <v>99216</v>
+        <v>99218</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4828,7 +4828,7 @@
         <v>137112303</v>
       </c>
       <c r="B38" t="n">
-        <v>101515</v>
+        <v>101518</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>

--- a/artfynd/A 37550-2026 artfynd.xlsx
+++ b/artfynd/A 37550-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137112312</v>
       </c>
       <c r="B2" t="n">
-        <v>92880</v>
+        <v>92885</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>137112280</v>
       </c>
       <c r="B3" t="n">
-        <v>92596</v>
+        <v>92601</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -911,7 +911,7 @@
         <v>137112282</v>
       </c>
       <c r="B4" t="n">
-        <v>92596</v>
+        <v>92601</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1023,7 +1023,7 @@
         <v>137257148</v>
       </c>
       <c r="B5" t="n">
-        <v>92596</v>
+        <v>92601</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1145,7 +1145,7 @@
         <v>137112301</v>
       </c>
       <c r="B6" t="n">
-        <v>80632</v>
+        <v>80637</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1257,7 +1257,7 @@
         <v>137257150</v>
       </c>
       <c r="B7" t="n">
-        <v>96627</v>
+        <v>96633</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1369,7 +1369,7 @@
         <v>137112287</v>
       </c>
       <c r="B8" t="n">
-        <v>93134</v>
+        <v>93140</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1486,7 +1486,7 @@
         <v>137112297</v>
       </c>
       <c r="B9" t="n">
-        <v>93134</v>
+        <v>93140</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1598,7 +1598,7 @@
         <v>137112308</v>
       </c>
       <c r="B10" t="n">
-        <v>92127</v>
+        <v>92132</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1710,7 +1710,7 @@
         <v>137112278</v>
       </c>
       <c r="B11" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1822,7 +1822,7 @@
         <v>137112285</v>
       </c>
       <c r="B12" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1934,7 +1934,7 @@
         <v>137112286</v>
       </c>
       <c r="B13" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2046,7 +2046,7 @@
         <v>137257147</v>
       </c>
       <c r="B14" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2172,7 +2172,7 @@
         <v>137257153</v>
       </c>
       <c r="B15" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2293,7 +2293,7 @@
         <v>137112283</v>
       </c>
       <c r="B16" t="n">
-        <v>80631</v>
+        <v>80636</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2405,7 +2405,7 @@
         <v>137112293</v>
       </c>
       <c r="B17" t="n">
-        <v>80631</v>
+        <v>80636</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2517,7 +2517,7 @@
         <v>137112300</v>
       </c>
       <c r="B18" t="n">
-        <v>80631</v>
+        <v>80636</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2629,7 +2629,7 @@
         <v>137257152</v>
       </c>
       <c r="B19" t="n">
-        <v>80631</v>
+        <v>80636</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2750,7 +2750,7 @@
         <v>137112296</v>
       </c>
       <c r="B20" t="n">
-        <v>80642</v>
+        <v>80647</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2862,7 +2862,7 @@
         <v>137112302</v>
       </c>
       <c r="B21" t="n">
-        <v>80642</v>
+        <v>80647</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2974,7 +2974,7 @@
         <v>137112305</v>
       </c>
       <c r="B22" t="n">
-        <v>80642</v>
+        <v>80647</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3086,7 +3086,7 @@
         <v>137257157</v>
       </c>
       <c r="B23" t="n">
-        <v>80642</v>
+        <v>80647</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3213,7 +3213,7 @@
         <v>137257158</v>
       </c>
       <c r="B24" t="n">
-        <v>80643</v>
+        <v>80648</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3340,7 +3340,7 @@
         <v>137112292</v>
       </c>
       <c r="B25" t="n">
-        <v>58031</v>
+        <v>58032</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3457,7 +3457,7 @@
         <v>137112306</v>
       </c>
       <c r="B26" t="n">
-        <v>58031</v>
+        <v>58032</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3574,7 +3574,7 @@
         <v>137112284</v>
       </c>
       <c r="B27" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3691,7 +3691,7 @@
         <v>137112288</v>
       </c>
       <c r="B28" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3808,7 +3808,7 @@
         <v>137112323</v>
       </c>
       <c r="B29" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3920,7 +3920,7 @@
         <v>137257154</v>
       </c>
       <c r="B30" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4033,7 +4033,7 @@
         <v>137257155</v>
       </c>
       <c r="B31" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4151,7 +4151,7 @@
         <v>137257156</v>
       </c>
       <c r="B32" t="n">
-        <v>58195</v>
+        <v>58196</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4268,7 +4268,7 @@
         <v>137112309</v>
       </c>
       <c r="B33" t="n">
-        <v>58138</v>
+        <v>58139</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4492,7 +4492,7 @@
         <v>137257151</v>
       </c>
       <c r="B35" t="n">
-        <v>106550</v>
+        <v>106556</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4604,7 +4604,7 @@
         <v>137112295</v>
       </c>
       <c r="B36" t="n">
-        <v>98280</v>
+        <v>98286</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4716,7 +4716,7 @@
         <v>137112304</v>
       </c>
       <c r="B37" t="n">
-        <v>99218</v>
+        <v>99224</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4828,7 +4828,7 @@
         <v>137112303</v>
       </c>
       <c r="B38" t="n">
-        <v>101518</v>
+        <v>101524</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>

--- a/artfynd/A 37550-2026 artfynd.xlsx
+++ b/artfynd/A 37550-2026 artfynd.xlsx
@@ -4492,7 +4492,7 @@
         <v>137257151</v>
       </c>
       <c r="B35" t="n">
-        <v>106556</v>
+        <v>106557</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>

--- a/artfynd/A 37550-2026 artfynd.xlsx
+++ b/artfynd/A 37550-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137112312</v>
       </c>
       <c r="B2" t="n">
-        <v>92885</v>
+        <v>92897</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>137112280</v>
       </c>
       <c r="B3" t="n">
-        <v>92601</v>
+        <v>92613</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -911,7 +911,7 @@
         <v>137112282</v>
       </c>
       <c r="B4" t="n">
-        <v>92601</v>
+        <v>92613</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1023,7 +1023,7 @@
         <v>137257148</v>
       </c>
       <c r="B5" t="n">
-        <v>92601</v>
+        <v>92613</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1145,7 +1145,7 @@
         <v>137112301</v>
       </c>
       <c r="B6" t="n">
-        <v>80637</v>
+        <v>80648</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1257,7 +1257,7 @@
         <v>137257150</v>
       </c>
       <c r="B7" t="n">
-        <v>96633</v>
+        <v>96645</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1369,7 +1369,7 @@
         <v>137112287</v>
       </c>
       <c r="B8" t="n">
-        <v>93140</v>
+        <v>93152</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1486,7 +1486,7 @@
         <v>137112297</v>
       </c>
       <c r="B9" t="n">
-        <v>93140</v>
+        <v>93152</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1598,7 +1598,7 @@
         <v>137112308</v>
       </c>
       <c r="B10" t="n">
-        <v>92132</v>
+        <v>92144</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1710,7 +1710,7 @@
         <v>137112278</v>
       </c>
       <c r="B11" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1822,7 +1822,7 @@
         <v>137112285</v>
       </c>
       <c r="B12" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1934,7 +1934,7 @@
         <v>137112286</v>
       </c>
       <c r="B13" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2046,7 +2046,7 @@
         <v>137257147</v>
       </c>
       <c r="B14" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2172,7 +2172,7 @@
         <v>137257153</v>
       </c>
       <c r="B15" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2293,7 +2293,7 @@
         <v>137112283</v>
       </c>
       <c r="B16" t="n">
-        <v>80636</v>
+        <v>80647</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2405,7 +2405,7 @@
         <v>137112293</v>
       </c>
       <c r="B17" t="n">
-        <v>80636</v>
+        <v>80647</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2517,7 +2517,7 @@
         <v>137112300</v>
       </c>
       <c r="B18" t="n">
-        <v>80636</v>
+        <v>80647</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2629,7 +2629,7 @@
         <v>137257152</v>
       </c>
       <c r="B19" t="n">
-        <v>80636</v>
+        <v>80647</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2750,7 +2750,7 @@
         <v>137112296</v>
       </c>
       <c r="B20" t="n">
-        <v>80647</v>
+        <v>80658</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2862,7 +2862,7 @@
         <v>137112302</v>
       </c>
       <c r="B21" t="n">
-        <v>80647</v>
+        <v>80658</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2974,7 +2974,7 @@
         <v>137112305</v>
       </c>
       <c r="B22" t="n">
-        <v>80647</v>
+        <v>80658</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3086,7 +3086,7 @@
         <v>137257157</v>
       </c>
       <c r="B23" t="n">
-        <v>80647</v>
+        <v>80658</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3213,7 +3213,7 @@
         <v>137257158</v>
       </c>
       <c r="B24" t="n">
-        <v>80648</v>
+        <v>80659</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -4492,7 +4492,7 @@
         <v>137257151</v>
       </c>
       <c r="B35" t="n">
-        <v>106557</v>
+        <v>106569</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4604,7 +4604,7 @@
         <v>137112295</v>
       </c>
       <c r="B36" t="n">
-        <v>98286</v>
+        <v>98298</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4716,7 +4716,7 @@
         <v>137112304</v>
       </c>
       <c r="B37" t="n">
-        <v>99224</v>
+        <v>99236</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4828,7 +4828,7 @@
         <v>137112303</v>
       </c>
       <c r="B38" t="n">
-        <v>101524</v>
+        <v>101536</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>

--- a/artfynd/A 37550-2026 artfynd.xlsx
+++ b/artfynd/A 37550-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137112312</v>
       </c>
       <c r="B2" t="n">
-        <v>92897</v>
+        <v>92898</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>137112280</v>
       </c>
       <c r="B3" t="n">
-        <v>92613</v>
+        <v>92614</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -911,7 +911,7 @@
         <v>137112282</v>
       </c>
       <c r="B4" t="n">
-        <v>92613</v>
+        <v>92614</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1023,7 +1023,7 @@
         <v>137257148</v>
       </c>
       <c r="B5" t="n">
-        <v>92613</v>
+        <v>92614</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1145,7 +1145,7 @@
         <v>137112301</v>
       </c>
       <c r="B6" t="n">
-        <v>80648</v>
+        <v>80649</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1257,7 +1257,7 @@
         <v>137257150</v>
       </c>
       <c r="B7" t="n">
-        <v>96645</v>
+        <v>96646</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1369,7 +1369,7 @@
         <v>137112287</v>
       </c>
       <c r="B8" t="n">
-        <v>93152</v>
+        <v>93153</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1486,7 +1486,7 @@
         <v>137112297</v>
       </c>
       <c r="B9" t="n">
-        <v>93152</v>
+        <v>93153</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1598,7 +1598,7 @@
         <v>137112308</v>
       </c>
       <c r="B10" t="n">
-        <v>92144</v>
+        <v>92145</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1710,7 +1710,7 @@
         <v>137112278</v>
       </c>
       <c r="B11" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1822,7 +1822,7 @@
         <v>137112285</v>
       </c>
       <c r="B12" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1934,7 +1934,7 @@
         <v>137112286</v>
       </c>
       <c r="B13" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2046,7 +2046,7 @@
         <v>137257147</v>
       </c>
       <c r="B14" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2172,7 +2172,7 @@
         <v>137257153</v>
       </c>
       <c r="B15" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2293,7 +2293,7 @@
         <v>137112283</v>
       </c>
       <c r="B16" t="n">
-        <v>80647</v>
+        <v>80648</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2405,7 +2405,7 @@
         <v>137112293</v>
       </c>
       <c r="B17" t="n">
-        <v>80647</v>
+        <v>80648</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2517,7 +2517,7 @@
         <v>137112300</v>
       </c>
       <c r="B18" t="n">
-        <v>80647</v>
+        <v>80648</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2629,7 +2629,7 @@
         <v>137257152</v>
       </c>
       <c r="B19" t="n">
-        <v>80647</v>
+        <v>80648</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2750,7 +2750,7 @@
         <v>137112296</v>
       </c>
       <c r="B20" t="n">
-        <v>80658</v>
+        <v>80659</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2862,7 +2862,7 @@
         <v>137112302</v>
       </c>
       <c r="B21" t="n">
-        <v>80658</v>
+        <v>80659</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2974,7 +2974,7 @@
         <v>137112305</v>
       </c>
       <c r="B22" t="n">
-        <v>80658</v>
+        <v>80659</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3086,7 +3086,7 @@
         <v>137257157</v>
       </c>
       <c r="B23" t="n">
-        <v>80658</v>
+        <v>80659</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3213,7 +3213,7 @@
         <v>137257158</v>
       </c>
       <c r="B24" t="n">
-        <v>80659</v>
+        <v>80660</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -4492,7 +4492,7 @@
         <v>137257151</v>
       </c>
       <c r="B35" t="n">
-        <v>106569</v>
+        <v>106570</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4604,7 +4604,7 @@
         <v>137112295</v>
       </c>
       <c r="B36" t="n">
-        <v>98298</v>
+        <v>98299</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4716,7 +4716,7 @@
         <v>137112304</v>
       </c>
       <c r="B37" t="n">
-        <v>99236</v>
+        <v>99237</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4828,7 +4828,7 @@
         <v>137112303</v>
       </c>
       <c r="B38" t="n">
-        <v>101536</v>
+        <v>101537</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>

--- a/artfynd/A 37550-2026 artfynd.xlsx
+++ b/artfynd/A 37550-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137112312</v>
       </c>
       <c r="B2" t="n">
-        <v>92898</v>
+        <v>92901</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>137112280</v>
       </c>
       <c r="B3" t="n">
-        <v>92614</v>
+        <v>92617</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -911,7 +911,7 @@
         <v>137112282</v>
       </c>
       <c r="B4" t="n">
-        <v>92614</v>
+        <v>92617</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1023,7 +1023,7 @@
         <v>137257148</v>
       </c>
       <c r="B5" t="n">
-        <v>92614</v>
+        <v>92617</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1145,7 +1145,7 @@
         <v>137112301</v>
       </c>
       <c r="B6" t="n">
-        <v>80649</v>
+        <v>80651</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1257,7 +1257,7 @@
         <v>137257150</v>
       </c>
       <c r="B7" t="n">
-        <v>96646</v>
+        <v>96649</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1369,7 +1369,7 @@
         <v>137112287</v>
       </c>
       <c r="B8" t="n">
-        <v>93153</v>
+        <v>93156</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1486,7 +1486,7 @@
         <v>137112297</v>
       </c>
       <c r="B9" t="n">
-        <v>93153</v>
+        <v>93156</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1598,7 +1598,7 @@
         <v>137112308</v>
       </c>
       <c r="B10" t="n">
-        <v>92145</v>
+        <v>92148</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1710,7 +1710,7 @@
         <v>137112278</v>
       </c>
       <c r="B11" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1822,7 +1822,7 @@
         <v>137112285</v>
       </c>
       <c r="B12" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1934,7 +1934,7 @@
         <v>137112286</v>
       </c>
       <c r="B13" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2046,7 +2046,7 @@
         <v>137257147</v>
       </c>
       <c r="B14" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2172,7 +2172,7 @@
         <v>137257153</v>
       </c>
       <c r="B15" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2293,7 +2293,7 @@
         <v>137112283</v>
       </c>
       <c r="B16" t="n">
-        <v>80648</v>
+        <v>80650</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2405,7 +2405,7 @@
         <v>137112293</v>
       </c>
       <c r="B17" t="n">
-        <v>80648</v>
+        <v>80650</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2517,7 +2517,7 @@
         <v>137112300</v>
       </c>
       <c r="B18" t="n">
-        <v>80648</v>
+        <v>80650</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2629,7 +2629,7 @@
         <v>137257152</v>
       </c>
       <c r="B19" t="n">
-        <v>80648</v>
+        <v>80650</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2750,7 +2750,7 @@
         <v>137112296</v>
       </c>
       <c r="B20" t="n">
-        <v>80659</v>
+        <v>80661</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2862,7 +2862,7 @@
         <v>137112302</v>
       </c>
       <c r="B21" t="n">
-        <v>80659</v>
+        <v>80661</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2974,7 +2974,7 @@
         <v>137112305</v>
       </c>
       <c r="B22" t="n">
-        <v>80659</v>
+        <v>80661</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3086,7 +3086,7 @@
         <v>137257157</v>
       </c>
       <c r="B23" t="n">
-        <v>80659</v>
+        <v>80661</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3213,7 +3213,7 @@
         <v>137257158</v>
       </c>
       <c r="B24" t="n">
-        <v>80660</v>
+        <v>80662</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -4492,7 +4492,7 @@
         <v>137257151</v>
       </c>
       <c r="B35" t="n">
-        <v>106570</v>
+        <v>106573</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4604,7 +4604,7 @@
         <v>137112295</v>
       </c>
       <c r="B36" t="n">
-        <v>98299</v>
+        <v>98302</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4716,7 +4716,7 @@
         <v>137112304</v>
       </c>
       <c r="B37" t="n">
-        <v>99237</v>
+        <v>99240</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4828,7 +4828,7 @@
         <v>137112303</v>
       </c>
       <c r="B38" t="n">
-        <v>101537</v>
+        <v>101540</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>

--- a/artfynd/A 37550-2026 artfynd.xlsx
+++ b/artfynd/A 37550-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137112312</v>
       </c>
       <c r="B2" t="n">
-        <v>92901</v>
+        <v>92905</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>137112280</v>
       </c>
       <c r="B3" t="n">
-        <v>92617</v>
+        <v>92621</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -911,7 +911,7 @@
         <v>137112282</v>
       </c>
       <c r="B4" t="n">
-        <v>92617</v>
+        <v>92621</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1023,7 +1023,7 @@
         <v>137257148</v>
       </c>
       <c r="B5" t="n">
-        <v>92617</v>
+        <v>92621</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1145,7 +1145,7 @@
         <v>137112301</v>
       </c>
       <c r="B6" t="n">
-        <v>80651</v>
+        <v>80655</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1257,7 +1257,7 @@
         <v>137257150</v>
       </c>
       <c r="B7" t="n">
-        <v>96649</v>
+        <v>96653</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1369,7 +1369,7 @@
         <v>137112287</v>
       </c>
       <c r="B8" t="n">
-        <v>93156</v>
+        <v>93160</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1486,7 +1486,7 @@
         <v>137112297</v>
       </c>
       <c r="B9" t="n">
-        <v>93156</v>
+        <v>93160</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1598,7 +1598,7 @@
         <v>137112308</v>
       </c>
       <c r="B10" t="n">
-        <v>92148</v>
+        <v>92152</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1710,7 +1710,7 @@
         <v>137112278</v>
       </c>
       <c r="B11" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1822,7 +1822,7 @@
         <v>137112285</v>
       </c>
       <c r="B12" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1934,7 +1934,7 @@
         <v>137112286</v>
       </c>
       <c r="B13" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2046,7 +2046,7 @@
         <v>137257147</v>
       </c>
       <c r="B14" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2172,7 +2172,7 @@
         <v>137257153</v>
       </c>
       <c r="B15" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2293,7 +2293,7 @@
         <v>137112283</v>
       </c>
       <c r="B16" t="n">
-        <v>80650</v>
+        <v>80654</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2405,7 +2405,7 @@
         <v>137112293</v>
       </c>
       <c r="B17" t="n">
-        <v>80650</v>
+        <v>80654</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2517,7 +2517,7 @@
         <v>137112300</v>
       </c>
       <c r="B18" t="n">
-        <v>80650</v>
+        <v>80654</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2629,7 +2629,7 @@
         <v>137257152</v>
       </c>
       <c r="B19" t="n">
-        <v>80650</v>
+        <v>80654</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2750,7 +2750,7 @@
         <v>137112296</v>
       </c>
       <c r="B20" t="n">
-        <v>80661</v>
+        <v>80665</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2862,7 +2862,7 @@
         <v>137112302</v>
       </c>
       <c r="B21" t="n">
-        <v>80661</v>
+        <v>80665</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2974,7 +2974,7 @@
         <v>137112305</v>
       </c>
       <c r="B22" t="n">
-        <v>80661</v>
+        <v>80665</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3086,7 +3086,7 @@
         <v>137257157</v>
       </c>
       <c r="B23" t="n">
-        <v>80661</v>
+        <v>80665</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3213,7 +3213,7 @@
         <v>137257158</v>
       </c>
       <c r="B24" t="n">
-        <v>80662</v>
+        <v>80666</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3340,7 +3340,7 @@
         <v>137112292</v>
       </c>
       <c r="B25" t="n">
-        <v>58032</v>
+        <v>58035</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3457,7 +3457,7 @@
         <v>137112306</v>
       </c>
       <c r="B26" t="n">
-        <v>58032</v>
+        <v>58035</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3574,7 +3574,7 @@
         <v>137112284</v>
       </c>
       <c r="B27" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3691,7 +3691,7 @@
         <v>137112288</v>
       </c>
       <c r="B28" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3808,7 +3808,7 @@
         <v>137112323</v>
       </c>
       <c r="B29" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3920,7 +3920,7 @@
         <v>137257154</v>
       </c>
       <c r="B30" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4033,7 +4033,7 @@
         <v>137257155</v>
       </c>
       <c r="B31" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4151,7 +4151,7 @@
         <v>137257156</v>
       </c>
       <c r="B32" t="n">
-        <v>58196</v>
+        <v>58199</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4268,7 +4268,7 @@
         <v>137112309</v>
       </c>
       <c r="B33" t="n">
-        <v>58139</v>
+        <v>58142</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4380,7 +4380,7 @@
         <v>137112311</v>
       </c>
       <c r="B34" t="n">
-        <v>56765</v>
+        <v>56768</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4492,7 +4492,7 @@
         <v>137257151</v>
       </c>
       <c r="B35" t="n">
-        <v>106573</v>
+        <v>106579</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4604,7 +4604,7 @@
         <v>137112295</v>
       </c>
       <c r="B36" t="n">
-        <v>98302</v>
+        <v>98306</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4716,7 +4716,7 @@
         <v>137112304</v>
       </c>
       <c r="B37" t="n">
-        <v>99240</v>
+        <v>99244</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4828,7 +4828,7 @@
         <v>137112303</v>
       </c>
       <c r="B38" t="n">
-        <v>101540</v>
+        <v>101544</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
